--- a/data/sample_exports/programmatic_dsp_export.xlsx
+++ b/data/sample_exports/programmatic_dsp_export.xlsx
@@ -502,28 +502,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2774.85</v>
+        <v>2806.03</v>
       </c>
       <c r="E2" t="n">
-        <v>462474</v>
+        <v>467672</v>
       </c>
       <c r="F2" t="n">
-        <v>1479</v>
+        <v>1403</v>
       </c>
       <c r="G2" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="H2" t="n">
-        <v>314482</v>
+        <v>336723</v>
       </c>
       <c r="I2" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="J2" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="K2" t="n">
-        <v>38.54</v>
+        <v>73.84</v>
       </c>
     </row>
     <row r="3">
@@ -543,28 +543,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2648.87</v>
+        <v>2785.37</v>
       </c>
       <c r="E3" t="n">
-        <v>441478</v>
+        <v>464228</v>
       </c>
       <c r="F3" t="n">
-        <v>1412</v>
+        <v>1764</v>
       </c>
       <c r="G3" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="H3" t="n">
-        <v>300205</v>
+        <v>338886</v>
       </c>
       <c r="I3" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="J3" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K3" t="n">
-        <v>41.39</v>
+        <v>39.79</v>
       </c>
     </row>
     <row r="4">
@@ -584,19 +584,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2901.28</v>
+        <v>2832.07</v>
       </c>
       <c r="E4" t="n">
-        <v>483545</v>
+        <v>472011</v>
       </c>
       <c r="F4" t="n">
-        <v>1789</v>
+        <v>1888</v>
       </c>
       <c r="G4" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="H4" t="n">
-        <v>333646</v>
+        <v>325687</v>
       </c>
       <c r="I4" t="n">
         <v>0.6899999999999999</v>
@@ -605,7 +605,7 @@
         <v>88</v>
       </c>
       <c r="K4" t="n">
-        <v>32.97</v>
+        <v>32.18</v>
       </c>
     </row>
     <row r="5">
@@ -625,28 +625,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2951.21</v>
+        <v>2873.68</v>
       </c>
       <c r="E5" t="n">
-        <v>491868</v>
+        <v>478946</v>
       </c>
       <c r="F5" t="n">
-        <v>1918</v>
+        <v>1676</v>
       </c>
       <c r="G5" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="H5" t="n">
-        <v>216421</v>
+        <v>205946</v>
       </c>
       <c r="I5" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="J5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K5" t="n">
-        <v>40.43</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="6">
@@ -666,28 +666,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2801.61</v>
+        <v>2933.46</v>
       </c>
       <c r="E6" t="n">
-        <v>466934</v>
+        <v>488910</v>
       </c>
       <c r="F6" t="n">
-        <v>1774</v>
+        <v>1857</v>
       </c>
       <c r="G6" t="n">
         <v>0.38</v>
       </c>
       <c r="H6" t="n">
-        <v>214789</v>
+        <v>195564</v>
       </c>
       <c r="I6" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="J6" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K6" t="n">
-        <v>43.78</v>
+        <v>46.56</v>
       </c>
     </row>
     <row r="7">
@@ -707,28 +707,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2881.87</v>
+        <v>2715.07</v>
       </c>
       <c r="E7" t="n">
-        <v>480311</v>
+        <v>452512</v>
       </c>
       <c r="F7" t="n">
-        <v>1681</v>
+        <v>1629</v>
       </c>
       <c r="G7" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H7" t="n">
-        <v>192124</v>
+        <v>194580</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="J7" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="K7" t="n">
-        <v>62.65</v>
+        <v>38.79</v>
       </c>
     </row>
     <row r="8">
@@ -748,28 +748,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2846.25</v>
+        <v>2842.59</v>
       </c>
       <c r="E8" t="n">
-        <v>474375</v>
+        <v>473764</v>
       </c>
       <c r="F8" t="n">
-        <v>1802</v>
+        <v>1563</v>
       </c>
       <c r="G8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="H8" t="n">
-        <v>208725</v>
+        <v>194243</v>
       </c>
       <c r="I8" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="J8" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="K8" t="n">
-        <v>44.47</v>
+        <v>83.61</v>
       </c>
     </row>
     <row r="9">
@@ -789,28 +789,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2724.26</v>
+        <v>2723.3</v>
       </c>
       <c r="E9" t="n">
-        <v>454044</v>
+        <v>453882</v>
       </c>
       <c r="F9" t="n">
-        <v>1407</v>
+        <v>1497</v>
       </c>
       <c r="G9" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="H9" t="n">
-        <v>181617</v>
+        <v>177013</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="J9" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="K9" t="n">
-        <v>68.11</v>
+        <v>50.43</v>
       </c>
     </row>
     <row r="10">
@@ -830,28 +830,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3522.11</v>
+        <v>3483.9</v>
       </c>
       <c r="E10" t="n">
-        <v>587019</v>
+        <v>580650</v>
       </c>
       <c r="F10" t="n">
-        <v>2054</v>
+        <v>2148</v>
       </c>
       <c r="G10" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="H10" t="n">
-        <v>381562</v>
+        <v>365809</v>
       </c>
       <c r="I10" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="J10" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="K10" t="n">
-        <v>71.88</v>
+        <v>39.59</v>
       </c>
     </row>
     <row r="11">
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3683.79</v>
+        <v>3560.08</v>
       </c>
       <c r="E11" t="n">
-        <v>613964</v>
+        <v>593347</v>
       </c>
       <c r="F11" t="n">
-        <v>2271</v>
+        <v>2076</v>
       </c>
       <c r="G11" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="H11" t="n">
-        <v>411355</v>
+        <v>385675</v>
       </c>
       <c r="I11" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="J11" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="K11" t="n">
-        <v>75.18000000000001</v>
+        <v>53.14</v>
       </c>
     </row>
     <row r="12">
@@ -912,28 +912,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3618.41</v>
+        <v>3565.5</v>
       </c>
       <c r="E12" t="n">
-        <v>603068</v>
+        <v>594250</v>
       </c>
       <c r="F12" t="n">
-        <v>2050</v>
+        <v>2317</v>
       </c>
       <c r="G12" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="H12" t="n">
-        <v>404055</v>
+        <v>415975</v>
       </c>
       <c r="I12" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="J12" t="n">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="K12" t="n">
-        <v>68.27</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="13">
@@ -953,28 +953,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3774.89</v>
+        <v>3754.11</v>
       </c>
       <c r="E13" t="n">
-        <v>629148</v>
+        <v>625684</v>
       </c>
       <c r="F13" t="n">
-        <v>2264</v>
+        <v>2377</v>
       </c>
       <c r="G13" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="H13" t="n">
-        <v>452986</v>
+        <v>394180</v>
       </c>
       <c r="I13" t="n">
-        <v>0.72</v>
+        <v>0.63</v>
       </c>
       <c r="J13" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="K13" t="n">
-        <v>41.03</v>
+        <v>50.73</v>
       </c>
     </row>
     <row r="14">
@@ -994,28 +994,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3714.74</v>
+        <v>3535.96</v>
       </c>
       <c r="E14" t="n">
-        <v>619122</v>
+        <v>589326</v>
       </c>
       <c r="F14" t="n">
-        <v>2105</v>
+        <v>2239</v>
       </c>
       <c r="G14" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="H14" t="n">
-        <v>408620</v>
+        <v>430207</v>
       </c>
       <c r="I14" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="J14" t="n">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="K14" t="n">
-        <v>88.45</v>
+        <v>34.67</v>
       </c>
     </row>
     <row r="15">
@@ -1035,28 +1035,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3709.5</v>
+        <v>3565.02</v>
       </c>
       <c r="E15" t="n">
-        <v>618250</v>
+        <v>594169</v>
       </c>
       <c r="F15" t="n">
-        <v>2411</v>
+        <v>2257</v>
       </c>
       <c r="G15" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="H15" t="n">
-        <v>414227</v>
+        <v>409976</v>
       </c>
       <c r="I15" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="K15" t="n">
-        <v>31.71</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="16">
@@ -1076,28 +1076,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3706.93</v>
+        <v>3479.27</v>
       </c>
       <c r="E16" t="n">
-        <v>617821</v>
+        <v>579878</v>
       </c>
       <c r="F16" t="n">
-        <v>2162</v>
+        <v>1855</v>
       </c>
       <c r="G16" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="H16" t="n">
-        <v>401583</v>
+        <v>365323</v>
       </c>
       <c r="I16" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="J16" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="K16" t="n">
-        <v>45.21</v>
+        <v>57.04</v>
       </c>
     </row>
     <row r="17">
@@ -1117,28 +1117,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3478.79</v>
+        <v>3529.21</v>
       </c>
       <c r="E17" t="n">
-        <v>579798</v>
+        <v>588201</v>
       </c>
       <c r="F17" t="n">
-        <v>1971</v>
+        <v>2176</v>
       </c>
       <c r="G17" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="H17" t="n">
-        <v>382666</v>
+        <v>376448</v>
       </c>
       <c r="I17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="J17" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="K17" t="n">
-        <v>84.84999999999999</v>
+        <v>51.15</v>
       </c>
     </row>
   </sheetData>
